--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBAD8E5-F984-44F3-8A60-7BA4532451C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28D66A1-CE3B-4F6D-966D-0A8D57F79497}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" activeTab="4" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,14 @@
     <sheet name="Invalidate_QR" sheetId="6" r:id="rId6"/>
     <sheet name="Reassign_Batch_QR" sheetId="7" r:id="rId7"/>
     <sheet name="QR_Monitoring_Filters" sheetId="8" r:id="rId8"/>
-    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId9"/>
-    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId10"/>
-    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId11"/>
-    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId12"/>
-    <sheet name="Batch_status_report" sheetId="13" r:id="rId13"/>
-    <sheet name="LoginData" sheetId="14" r:id="rId14"/>
+    <sheet name="schedule_report_create" sheetId="15" r:id="rId9"/>
+    <sheet name="schedule_report_filters" sheetId="16" r:id="rId10"/>
+    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId11"/>
+    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId12"/>
+    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId13"/>
+    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId14"/>
+    <sheet name="Batch_status_report" sheetId="13" r:id="rId15"/>
+    <sheet name="LoginData" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
   <si>
     <t>product_name</t>
   </si>
@@ -293,6 +295,30 @@
   </si>
   <si>
     <t>B155-1002</t>
+  </si>
+  <si>
+    <t>select_report</t>
+  </si>
+  <si>
+    <t>mail_receiving_duration</t>
+  </si>
+  <si>
+    <t>Scan Analytics Report</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>date_string</t>
+  </si>
+  <si>
+    <t>scan_analytics_report</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
 </sst>
 </file>
@@ -412,7 +438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -468,6 +494,14 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -820,6 +854,134 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45BFDFC-65AA-4BDE-AEB9-A94D13C42CBE}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="28">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805A6EDD-E425-4375-9798-049A39968A7E}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BF2E4E-D2AD-4788-84CE-589D65DD9913}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -871,7 +1033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C593467-91D7-45A0-AB4C-29552EB2F315}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -908,7 +1070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE76918-F0A7-4D6C-A220-F9B93E3F4D71}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -935,7 +1097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8812D42C-EE85-4119-BC63-85E0A2A59C8A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -973,7 +1135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9810B8-64D0-4E9C-8574-FE25F4330D20}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1583,57 +1745,77 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805A6EDD-E425-4375-9798-049A39968A7E}">
-  <dimension ref="A1:D5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47321248-6969-4F5E-944C-613388F81213}">
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    <row r="1" spans="1:10">
+      <c r="A1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="E16" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28D66A1-CE3B-4F6D-966D-0A8D57F79497}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AD835A-3C92-4B48-8B6E-8D0C2B326181}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
@@ -315,10 +315,10 @@
     <t>date_string</t>
   </si>
   <si>
-    <t>scan_analytics_report</t>
-  </si>
-  <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>amar</t>
   </si>
 </sst>
 </file>
@@ -880,16 +880,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="28">
-        <v>46074</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AD835A-3C92-4B48-8B6E-8D0C2B326181}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3720E3D7-EE51-46A9-BB79-33BDDB80CBA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
@@ -318,7 +318,7 @@
     <t>All</t>
   </si>
   <si>
-    <t>amar</t>
+    <t>scan_analytics_report</t>
   </si>
 </sst>
 </file>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3720E3D7-EE51-46A9-BB79-33BDDB80CBA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43226C55-0705-4558-86FB-C302957E11FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="17" activeTab="20" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -23,12 +23,17 @@
     <sheet name="QR_Monitoring_Filters" sheetId="8" r:id="rId8"/>
     <sheet name="schedule_report_create" sheetId="15" r:id="rId9"/>
     <sheet name="schedule_report_filters" sheetId="16" r:id="rId10"/>
-    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId11"/>
-    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId12"/>
-    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId13"/>
-    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId14"/>
-    <sheet name="Batch_status_report" sheetId="13" r:id="rId15"/>
-    <sheet name="LoginData" sheetId="14" r:id="rId16"/>
+    <sheet name="Sheet1" sheetId="17" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="18" r:id="rId12"/>
+    <sheet name="Sheet3" sheetId="19" r:id="rId13"/>
+    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId14"/>
+    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId15"/>
+    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId16"/>
+    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId17"/>
+    <sheet name="Batch_status_report" sheetId="13" r:id="rId18"/>
+    <sheet name="LoginData" sheetId="14" r:id="rId19"/>
+    <sheet name="Roles_and_permission_create" sheetId="20" r:id="rId20"/>
+    <sheet name="Roles_and_permission_filters" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="104">
   <si>
     <t>product_name</t>
   </si>
@@ -319,6 +324,39 @@
   </si>
   <si>
     <t>scan_analytics_report</t>
+  </si>
+  <si>
+    <t>Role_name</t>
+  </si>
+  <si>
+    <t>User_type</t>
+  </si>
+  <si>
+    <t>Admin User - Manufacturer</t>
+  </si>
+  <si>
+    <t>lkjhgfwe</t>
+  </si>
+  <si>
+    <t>poiuyq</t>
+  </si>
+  <si>
+    <t>search_name</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>qwerty</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
   </si>
 </sst>
 </file>
@@ -923,6 +961,33 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719DE049-13A9-41AD-8D77-209B4D420600}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B36C8-07D8-43F3-947E-E60737F16168}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530E70C9-470C-48D5-826C-6E6296487FE3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805A6EDD-E425-4375-9798-049A39968A7E}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -981,7 +1046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BF2E4E-D2AD-4788-84CE-589D65DD9913}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1033,7 +1098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C593467-91D7-45A0-AB4C-29552EB2F315}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1070,7 +1135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE76918-F0A7-4D6C-A220-F9B93E3F4D71}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1097,7 +1162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8812D42C-EE85-4119-BC63-85E0A2A59C8A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1135,7 +1200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9810B8-64D0-4E9C-8574-FE25F4330D20}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1235,6 +1300,136 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F558A45-F57B-4E55-9D43-AC432A6721A1}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43879EE9-C99F-4A5B-96F3-E1D0A9776555}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43226C55-0705-4558-86FB-C302957E11FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B34A324-3516-40B0-A1BE-99946A4E667A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3405" windowWidth="21600" windowHeight="6675" firstSheet="17" activeTab="20" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="2250" yWindow="4305" windowWidth="17070" windowHeight="8205" firstSheet="19" activeTab="21" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="LoginData" sheetId="14" r:id="rId19"/>
     <sheet name="Roles_and_permission_create" sheetId="20" r:id="rId20"/>
     <sheet name="Roles_and_permission_filters" sheetId="21" r:id="rId21"/>
+    <sheet name="users_create" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
   <si>
     <t>product_name</t>
   </si>
@@ -335,9 +336,6 @@
     <t>Admin User - Manufacturer</t>
   </si>
   <si>
-    <t>lkjhgfwe</t>
-  </si>
-  <si>
     <t>poiuyq</t>
   </si>
   <si>
@@ -350,13 +348,31 @@
     <t>2026-02-27</t>
   </si>
   <si>
-    <t>qwerty</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>select_Role</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mobile_number</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>Asdfg@123</t>
+  </si>
+  <si>
+    <t>testing (Arihant)</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>abcd123416790@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -476,7 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -540,6 +556,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1328,7 +1345,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>95</v>
@@ -1376,7 +1393,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>6</v>
@@ -1390,31 +1407,23 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>103</v>
-      </c>
+      <c r="A3" s="16"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3"/>
@@ -1432,6 +1441,109 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08D1696-D02C-4610-92E6-D56A7B92D2A5}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="40.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3">
+        <v>9876526895</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="29"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{0CD11CE9-983E-41B9-A5E5-B10B0A2421B6}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{1DB92A8A-74BC-47C3-88C8-2F27DCE43581}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B34A324-3516-40B0-A1BE-99946A4E667A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB214BB-6323-4410-AF94-88869DB5D30C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="4305" windowWidth="17070" windowHeight="8205" firstSheet="19" activeTab="21" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="840" yWindow="4095" windowWidth="17070" windowHeight="8205" firstSheet="20" activeTab="22" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="Roles_and_permission_create" sheetId="20" r:id="rId20"/>
     <sheet name="Roles_and_permission_filters" sheetId="21" r:id="rId21"/>
     <sheet name="users_create" sheetId="22" r:id="rId22"/>
+    <sheet name="user_filters" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="111">
   <si>
     <t>product_name</t>
   </si>
@@ -369,10 +370,16 @@
     <t>testing (Arihant)</t>
   </si>
   <si>
-    <t>demo</t>
-  </si>
-  <si>
-    <t>abcd123416790@gmail.com</t>
+    <t>abcd1234316790@gmail.com</t>
+  </si>
+  <si>
+    <t>demotest</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
   </si>
 </sst>
 </file>
@@ -492,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -557,6 +564,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1345,7 +1353,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>95</v>
@@ -1485,13 +1493,13 @@
         <v>106</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="3">
-        <v>9876526895</v>
+        <v>9876521895</v>
       </c>
       <c r="F2" s="29" t="s">
         <v>105</v>
@@ -1543,6 +1551,74 @@
     <hyperlink ref="C2" r:id="rId1" xr:uid="{0CD11CE9-983E-41B9-A5E5-B10B0A2421B6}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{1DB92A8A-74BC-47C3-88C8-2F27DCE43581}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6FDA5E-64D6-4D8A-A7B1-583E8820775D}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB214BB-6323-4410-AF94-88869DB5D30C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28719CE1-B1F6-4A2C-BA97-093F9AAB56E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="4095" windowWidth="17070" windowHeight="8205" firstSheet="20" activeTab="22" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="7950" yWindow="2595" windowWidth="17070" windowHeight="8205" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="110">
   <si>
     <t>product_name</t>
   </si>
@@ -76,12 +76,6 @@
     <t>country</t>
   </si>
   <si>
-    <t>variant_type</t>
-  </si>
-  <si>
-    <t>variant_value</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -133,12 +127,6 @@
     <t>1.5 cm</t>
   </si>
   <si>
-    <t>lenskart</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -157,9 +145,6 @@
     <t>blue</t>
   </si>
   <si>
-    <t>glass</t>
-  </si>
-  <si>
     <t>search_value</t>
   </si>
   <si>
@@ -268,42 +253,21 @@
     <t>QR Code with Microtext and Invisible Text</t>
   </si>
   <si>
-    <t>service</t>
-  </si>
-  <si>
     <t>sample123@gmail.com</t>
   </si>
   <si>
     <t>test@123</t>
   </si>
   <si>
-    <t>sample</t>
-  </si>
-  <si>
     <t>test</t>
   </si>
   <si>
-    <t>waterbottle</t>
-  </si>
-  <si>
-    <t>PRD2025X0004</t>
-  </si>
-  <si>
-    <t>B155-1001</t>
-  </si>
-  <si>
     <t>chair</t>
   </si>
   <si>
     <t>plastic</t>
   </si>
   <si>
-    <t>PRD2025X0005</t>
-  </si>
-  <si>
-    <t>B155-1002</t>
-  </si>
-  <si>
     <t>select_report</t>
   </si>
   <si>
@@ -380,6 +344,39 @@
   </si>
   <si>
     <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>QR_Type</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>image_format</t>
+  </si>
+  <si>
+    <t>M155-MPGH-0087</t>
+  </si>
+  <si>
+    <t>PRD2025X0007</t>
+  </si>
+  <si>
+    <t>B794-50</t>
+  </si>
+  <si>
+    <t>le beta</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>speakers</t>
+  </si>
+  <si>
+    <t>speakercovers</t>
   </si>
 </sst>
 </file>
@@ -888,26 +885,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -929,27 +926,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D2" s="28">
         <v>46077</v>
@@ -1025,26 +1022,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1084,26 +1081,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1135,13 +1132,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1152,7 +1149,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1170,12 +1167,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1199,24 +1196,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1236,39 +1233,39 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="21" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1293,35 +1290,35 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1342,10 +1339,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1353,13 +1350,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1401,30 +1398,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1467,42 +1464,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3">
         <v>9876521895</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1568,30 +1565,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="19" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="30" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1632,9 +1629,8 @@
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="5" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="37.140625" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" customWidth="1"/>
@@ -1658,10 +1654,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>6</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>7</v>
@@ -1669,82 +1665,52 @@
       <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="47.25">
-      <c r="A3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="J2" s="13"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1"/>
@@ -1786,16 +1752,15 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{8B51A6DA-AB47-4D21-B79F-C0F5CD9F6D1E}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{AB223196-CF71-46C6-A72C-98AA00DBB8D9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A9F92-C77C-4D8F-B88E-7CF0AEB70FC5}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -1807,46 +1772,50 @@
     <col min="7" max="7" width="16.85546875" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
     <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5">
+    <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30">
+      <c r="A2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1234</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="30">
-      <c r="A2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1002</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -1858,45 +1827,31 @@
         <v>46374</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="30">
-      <c r="A3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="5">
-        <v>1001</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
-        <v>45423</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46375</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>67</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1906,7 +1861,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1916,7 +1871,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="D12" s="23"/>
     </row>
   </sheetData>
@@ -1937,7 +1892,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>6</v>
@@ -1945,21 +1900,22 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>80</v>
+      <c r="A3" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1975,7 +1931,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>6</v>
@@ -1983,18 +1939,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2015,44 +1971,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2075,42 +2031,46 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="5">
+        <v>9619583752</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>51</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2140,30 +2100,30 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:10">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28719CE1-B1F6-4A2C-BA97-093F9AAB56E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D85626-4F48-4572-A113-448FFDB2F846}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7950" yWindow="2595" windowWidth="17070" windowHeight="8205" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -23,19 +23,16 @@
     <sheet name="QR_Monitoring_Filters" sheetId="8" r:id="rId8"/>
     <sheet name="schedule_report_create" sheetId="15" r:id="rId9"/>
     <sheet name="schedule_report_filters" sheetId="16" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="17" r:id="rId11"/>
-    <sheet name="Sheet2" sheetId="18" r:id="rId12"/>
-    <sheet name="Sheet3" sheetId="19" r:id="rId13"/>
-    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId14"/>
-    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId15"/>
-    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId16"/>
-    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId17"/>
-    <sheet name="Batch_status_report" sheetId="13" r:id="rId18"/>
-    <sheet name="LoginData" sheetId="14" r:id="rId19"/>
-    <sheet name="Roles_and_permission_create" sheetId="20" r:id="rId20"/>
-    <sheet name="Roles_and_permission_filters" sheetId="21" r:id="rId21"/>
-    <sheet name="users_create" sheetId="22" r:id="rId22"/>
-    <sheet name="user_filters" sheetId="23" r:id="rId23"/>
+    <sheet name="QR_Monitoring_Filter_By_field" sheetId="11" r:id="rId11"/>
+    <sheet name="QR_Monitoring_fake_product_fdb" sheetId="12" r:id="rId12"/>
+    <sheet name="QR_Monitoring_export_ID_based" sheetId="9" r:id="rId13"/>
+    <sheet name="QR_Monitoring_export_Bulk_ID" sheetId="10" r:id="rId14"/>
+    <sheet name="Reports" sheetId="13" r:id="rId15"/>
+    <sheet name="LoginData" sheetId="14" r:id="rId16"/>
+    <sheet name="Roles_and_permission_create" sheetId="20" r:id="rId17"/>
+    <sheet name="Roles_and_permission_filters" sheetId="21" r:id="rId18"/>
+    <sheet name="users_create" sheetId="22" r:id="rId19"/>
+    <sheet name="user_filters" sheetId="23" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
   <si>
     <t>product_name</t>
   </si>
@@ -139,9 +136,6 @@
     <t>variants_value</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
     <t>blue</t>
   </si>
   <si>
@@ -262,27 +256,12 @@
     <t>test</t>
   </si>
   <si>
-    <t>chair</t>
-  </si>
-  <si>
-    <t>plastic</t>
-  </si>
-  <si>
     <t>select_report</t>
   </si>
   <si>
     <t>mail_receiving_duration</t>
   </si>
   <si>
-    <t>Scan Analytics Report</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>date_string</t>
   </si>
   <si>
@@ -301,18 +280,9 @@
     <t>Admin User - Manufacturer</t>
   </si>
   <si>
-    <t>poiuyq</t>
-  </si>
-  <si>
     <t>search_name</t>
   </si>
   <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
     <t>user_name</t>
   </si>
   <si>
@@ -334,18 +304,9 @@
     <t>testing (Arihant)</t>
   </si>
   <si>
-    <t>abcd1234316790@gmail.com</t>
-  </si>
-  <si>
-    <t>demotest</t>
-  </si>
-  <si>
     <t>2026-03-01</t>
   </si>
   <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
     <t>QR_Type</t>
   </si>
   <si>
@@ -358,9 +319,6 @@
     <t>M155-MPGH-0087</t>
   </si>
   <si>
-    <t>PRD2025X0007</t>
-  </si>
-  <si>
     <t>B794-50</t>
   </si>
   <si>
@@ -373,10 +331,76 @@
     <t>2025-12-01</t>
   </si>
   <si>
-    <t>speakers</t>
-  </si>
-  <si>
-    <t>speakercovers</t>
+    <t>video_title</t>
+  </si>
+  <si>
+    <t>video_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testing </t>
+  </si>
+  <si>
+    <t>C:\Users\Suresh V\Downloads\20260505_094627.mp4</t>
+  </si>
+  <si>
+    <t>testt</t>
+  </si>
+  <si>
+    <t>sheet</t>
+  </si>
+  <si>
+    <t>sheett</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>paperr</t>
+  </si>
+  <si>
+    <t>mklp</t>
+  </si>
+  <si>
+    <t>mklpo</t>
+  </si>
+  <si>
+    <t>plasticssss</t>
+  </si>
+  <si>
+    <t>0024</t>
+  </si>
+  <si>
+    <t>PRD2026X00018</t>
+  </si>
+  <si>
+    <t>PRD2026X00019</t>
+  </si>
+  <si>
+    <t>Print Audit Report</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>Bi-Weekly</t>
+  </si>
+  <si>
+    <t>samples</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>abcd12316790@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-05-8</t>
   </si>
 </sst>
 </file>
@@ -526,9 +550,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -562,6 +583,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -880,7 +904,7 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
@@ -893,7 +917,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
@@ -901,9 +925,9 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -926,29 +950,29 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="28">
+        <v>58</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="27">
         <v>46077</v>
       </c>
     </row>
@@ -983,33 +1007,6 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719DE049-13A9-41AD-8D77-209B4D420600}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B36C8-07D8-43F3-947E-E60737F16168}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530E70C9-470C-48D5-826C-6E6296487FE3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805A6EDD-E425-4375-9798-049A39968A7E}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1021,27 +1018,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>54</v>
+      <c r="C2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1068,7 +1065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BF2E4E-D2AD-4788-84CE-589D65DD9913}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1080,27 +1077,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="C2" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>54</v>
+      <c r="C2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1120,7 +1117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C593467-91D7-45A0-AB4C-29552EB2F315}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1132,13 +1129,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1149,7 +1146,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1157,22 +1154,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE76918-F0A7-4D6C-A220-F9B93E3F4D71}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1184,7 +1181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8812D42C-EE85-4119-BC63-85E0A2A59C8A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1195,25 +1192,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9810B8-64D0-4E9C-8574-FE25F4330D20}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1232,40 +1229,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>66</v>
+      <c r="A1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1278,56 +1275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49965304-110C-43B7-8F15-D1A55CEFA51D}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
-      <c r="A1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F558A45-F57B-4E55-9D43-AC432A6721A1}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1339,10 +1287,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1350,10 +1298,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1385,7 +1333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43879EE9-C99F-4A5B-96F3-E1D0A9776555}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1397,38 +1345,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16" t="s">
-        <v>84</v>
+      <c r="A2" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>87</v>
+        <v>73</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3"/>
@@ -1449,7 +1397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08D1696-D02C-4610-92E6-D56A7B92D2A5}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1464,51 +1412,51 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>95</v>
+        <v>85</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>117</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3">
-        <v>9876521895</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>93</v>
+        <v>9807521895</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="29"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="29"/>
+      <c r="F3" s="28"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3"/>
@@ -1552,7 +1500,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49965304-110C-43B7-8F15-D1A55CEFA51D}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75">
+      <c r="A1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6FDA5E-64D6-4D8A-A7B1-583E8820775D}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1564,31 +1561,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="30" t="s">
-        <v>92</v>
+      <c r="A2" s="29" t="s">
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>98</v>
+        <v>73</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1633,8 +1630,8 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="37.140625" customWidth="1"/>
     <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5">
@@ -1665,15 +1662,19 @@
       <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="J1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>13</v>
@@ -1682,13 +1683,13 @@
         <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -1696,21 +1697,47 @@
       <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="11"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="11"/>
+      <c r="J2" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="47.25">
+      <c r="A3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1"/>
@@ -1752,9 +1779,10 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{8B51A6DA-AB47-4D21-B79F-C0F5CD9F6D1E}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{7743F41D-75AB-44A3-B840-8FDE6759F018}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1800,16 +1828,16 @@
       <c r="H1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>101</v>
+      <c r="I1" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B2" s="5">
         <v>1234</v>
@@ -1833,10 +1861,10 @@
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1872,7 +1900,7 @@
       <c r="H5" s="1"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="D12" s="23"/>
+      <c r="D12" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1891,27 +1919,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1930,27 +1958,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1970,45 +1998,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30">
+      <c r="A2" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="30">
-      <c r="A2" s="16" t="s">
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30">
+      <c r="A3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="30">
-      <c r="A3" s="16" t="s">
+      <c r="D3" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2030,47 +2058,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="15"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>47</v>
+      <c r="C2" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>46</v>
+      <c r="C3" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2089,7 +2117,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47321248-6969-4F5E-944C-613388F81213}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -2098,69 +2126,57 @@
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>58</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="J3" s="20"/>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="E16" s="26"/>
+    <row r="14" spans="1:5">
+      <c r="E14" s="25"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D85626-4F48-4572-A113-448FFDB2F846}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9B26E1-E026-4579-A530-09DB589A42A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="19" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="9330" yWindow="3975" windowWidth="17070" windowHeight="8205" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="121">
   <si>
     <t>product_name</t>
   </si>
@@ -223,9 +223,6 @@
     <t>CSV</t>
   </si>
   <si>
-    <t>Last 90 Days</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
     <t>All</t>
   </si>
   <si>
-    <t>scan_analytics_report</t>
-  </si>
-  <si>
     <t>Role_name</t>
   </si>
   <si>
@@ -301,12 +295,6 @@
     <t>Asdfg@123</t>
   </si>
   <si>
-    <t>testing (Arihant)</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>QR_Type</t>
   </si>
   <si>
@@ -346,9 +334,6 @@
     <t>testt</t>
   </si>
   <si>
-    <t>sheet</t>
-  </si>
-  <si>
     <t>sheett</t>
   </si>
   <si>
@@ -358,9 +343,6 @@
     <t>paperr</t>
   </si>
   <si>
-    <t>mklp</t>
-  </si>
-  <si>
     <t>mklpo</t>
   </si>
   <si>
@@ -370,12 +352,6 @@
     <t>0024</t>
   </si>
   <si>
-    <t>PRD2026X00018</t>
-  </si>
-  <si>
-    <t>PRD2026X00019</t>
-  </si>
-  <si>
     <t>Print Audit Report</t>
   </si>
   <si>
@@ -385,22 +361,52 @@
     <t>Bi-Weekly</t>
   </si>
   <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>mklpp</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>abcd128316790@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>Last 7 Days</t>
+  </si>
+  <si>
+    <t>XLSX</t>
+  </si>
+  <si>
     <t>samples</t>
   </si>
   <si>
-    <t>demo</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>abcd12316790@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-05-8</t>
+    <t>PRD2026X00022</t>
+  </si>
+  <si>
+    <t>PRD2026X00023</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>print_audit_report</t>
   </si>
 </sst>
 </file>
@@ -917,7 +923,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
@@ -925,7 +931,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>9</v>
@@ -939,66 +945,99 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45BFDFC-65AA-4BDE-AEB9-A94D13C42CBE}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="27">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>120</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="27">
+        <v>46167</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1207,7 +1246,7 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -1233,36 +1272,36 @@
         <v>40</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>67</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1287,10 +1326,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1298,10 +1337,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1346,7 +1385,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
@@ -1360,16 +1399,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1412,42 +1451,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3">
-        <v>9807521895</v>
+        <v>9807529895</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1523,10 +1562,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -1534,10 +1573,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>101</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
@@ -1562,7 +1601,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
@@ -1576,16 +1615,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1663,18 +1702,18 @@
         <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>13</v>
@@ -1683,13 +1722,13 @@
         <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -1698,18 +1737,18 @@
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="47.25">
       <c r="A3" s="11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>13</v>
@@ -1718,13 +1757,13 @@
         <v>14</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>10</v>
@@ -1733,10 +1772,10 @@
         <v>11</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1829,15 +1868,15 @@
         <v>21</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B2" s="5">
         <v>1234</v>
@@ -1861,10 +1900,10 @@
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1936,7 +1975,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -2074,13 +2113,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>46</v>
@@ -2095,7 +2134,7 @@
         <v>9999999999</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>45</v>
@@ -2128,7 +2167,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>55</v>
@@ -2137,28 +2176,36 @@
         <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3"/>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9B26E1-E026-4579-A530-09DB589A42A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5269B435-8DC1-4B8B-A4A5-27746D726B92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9330" yWindow="3975" windowWidth="17070" windowHeight="8205" firstSheet="7" activeTab="9" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="120">
   <si>
     <t>product_name</t>
   </si>
@@ -112,9 +112,6 @@
     <t>delivery_location</t>
   </si>
   <si>
-    <t>Black</t>
-  </si>
-  <si>
     <t>sku_id</t>
   </si>
   <si>
@@ -304,9 +301,6 @@
     <t>image_format</t>
   </si>
   <si>
-    <t>M155-MPGH-0087</t>
-  </si>
-  <si>
     <t>B794-50</t>
   </si>
   <si>
@@ -403,10 +397,13 @@
     <t>2026-05-17</t>
   </si>
   <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
     <t>print_audit_report</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>M19342-PRD2025X0012</t>
   </si>
 </sst>
 </file>
@@ -915,15 +912,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
@@ -931,7 +928,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>9</v>
@@ -959,48 +956,48 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="E2" s="27">
         <v>46167</v>
       </c>
       <c r="F2" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>118</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1058,26 +1055,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1117,26 +1114,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1168,13 +1165,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>48</v>
-      </c>
-      <c r="C1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1185,7 +1182,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1203,12 +1200,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1232,24 +1229,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1269,39 +1266,39 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1326,10 +1323,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1337,10 +1334,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1385,30 +1382,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1451,33 +1448,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -1486,7 +1483,7 @@
         <v>9807529895</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1551,21 +1548,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -1573,13 +1570,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1601,30 +1598,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1690,7 +1687,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>5</v>
@@ -1702,18 +1699,18 @@
         <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>13</v>
@@ -1722,13 +1719,13 @@
         <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -1737,18 +1734,18 @@
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="47.25">
       <c r="A3" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>13</v>
@@ -1757,13 +1754,13 @@
         <v>14</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>10</v>
@@ -1772,10 +1769,10 @@
         <v>11</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1844,7 +1841,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>15</v>
@@ -1868,42 +1865,40 @@
         <v>21</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="B2" s="5">
-        <v>1234</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>22</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="6">
-        <v>45422</v>
+        <v>46162</v>
       </c>
       <c r="F2" s="6">
         <v>46374</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1959,7 +1954,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -1967,18 +1962,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +1993,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2006,18 +2001,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2038,13 +2033,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>16</v>
@@ -2052,30 +2047,30 @@
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2098,46 +2093,46 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>43</v>
       </c>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2167,44 +2162,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>104</v>
-      </c>
       <c r="D2" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5269B435-8DC1-4B8B-A4A5-27746D726B92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D4DFB8-6BD9-4F04-96F9-5B36C7F58D56}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <sheet name="users_create" sheetId="22" r:id="rId19"/>
     <sheet name="user_filters" sheetId="23" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="138">
   <si>
     <t>product_name</t>
   </si>
@@ -133,9 +133,6 @@
     <t>variants_value</t>
   </si>
   <si>
-    <t>blue</t>
-  </si>
-  <si>
     <t>search_value</t>
   </si>
   <si>
@@ -325,27 +322,12 @@
     <t>C:\Users\Suresh V\Downloads\20260505_094627.mp4</t>
   </si>
   <si>
-    <t>testt</t>
-  </si>
-  <si>
-    <t>sheett</t>
-  </si>
-  <si>
     <t>paper</t>
   </si>
   <si>
-    <t>paperr</t>
-  </si>
-  <si>
-    <t>mklpo</t>
-  </si>
-  <si>
     <t>plasticssss</t>
   </si>
   <si>
-    <t>0024</t>
-  </si>
-  <si>
     <t>Print Audit Report</t>
   </si>
   <si>
@@ -385,32 +367,104 @@
     <t>PRD2026X00022</t>
   </si>
   <si>
-    <t>PRD2026X00023</t>
-  </si>
-  <si>
     <t>Weekly</t>
   </si>
   <si>
     <t>15:00</t>
   </si>
   <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
     <t>print_audit_report</t>
   </si>
   <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
     <t>M19342-PRD2025X0012</t>
+  </si>
+  <si>
+    <t>filter_status</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>edit_category_name</t>
+  </si>
+  <si>
+    <t>edit_status</t>
+  </si>
+  <si>
+    <t>testingsample</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>search_Category</t>
+  </si>
+  <si>
+    <t>edit_variants_type</t>
+  </si>
+  <si>
+    <t>edit_variants_value</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>testingsampletestingsample</t>
+  </si>
+  <si>
+    <t>sampletesingg</t>
+  </si>
+  <si>
+    <t>edit_product_name</t>
+  </si>
+  <si>
+    <t>edit_brand_name</t>
+  </si>
+  <si>
+    <t>edit_upload_product_image</t>
+  </si>
+  <si>
+    <t>edit_product_url</t>
+  </si>
+  <si>
+    <t>edit_SKU_ID</t>
+  </si>
+  <si>
+    <t>edit_select_category</t>
+  </si>
+  <si>
+    <t>edit_description</t>
+  </si>
+  <si>
+    <t>edit_country</t>
+  </si>
+  <si>
+    <t>edit_video_title</t>
+  </si>
+  <si>
+    <t>edit_video_file</t>
+  </si>
+  <si>
+    <t>prdgvgftfg</t>
+  </si>
+  <si>
+    <t>filter_category</t>
+  </si>
+  <si>
+    <t>filter_created_by</t>
+  </si>
+  <si>
+    <t>asdad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +540,14 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -523,7 +585,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -587,6 +649,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -904,35 +983,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3EF5A8-6DCE-48C0-BCE9-54199AD6514E}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75">
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -956,48 +1114,48 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="27">
         <v>46167</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1055,26 +1213,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1114,26 +1272,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1165,13 +1323,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1182,7 +1340,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1200,12 +1358,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1229,24 +1387,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
-      </c>
-      <c r="B2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1266,39 +1424,39 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>65</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1323,10 +1481,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1334,10 +1492,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1382,30 +1540,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1448,33 +1606,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -1483,7 +1641,7 @@
         <v>9807529895</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1538,15 +1696,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49965304-110C-43B7-8F15-D1A55CEFA51D}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="13" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="39.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" customWidth="1"/>
+    <col min="9" max="9" width="29.140625" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
         <v>25</v>
       </c>
@@ -1556,28 +1720,52 @@
       <c r="C1" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" s="36"/>
+      <c r="G1" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1" s="35"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1598,30 +1786,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1655,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A4F18C-1025-45CE-9112-F55A683B9C13}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -1668,9 +1856,25 @@
     <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="20.42578125" customWidth="1"/>
     <col min="11" max="11" width="53.28515625" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" customWidth="1"/>
+    <col min="20" max="22" width="28.5703125" customWidth="1"/>
+    <col min="25" max="25" width="25.140625" customWidth="1"/>
+    <col min="26" max="26" width="19.42578125" customWidth="1"/>
+    <col min="27" max="27" width="33.5703125" customWidth="1"/>
+    <col min="28" max="28" width="20.7109375" customWidth="1"/>
+    <col min="29" max="29" width="23.140625" customWidth="1"/>
+    <col min="30" max="30" width="25.42578125" customWidth="1"/>
+    <col min="31" max="31" width="16.7109375" customWidth="1"/>
+    <col min="32" max="33" width="17.28515625" customWidth="1"/>
+    <col min="34" max="34" width="25.42578125" customWidth="1"/>
+    <col min="35" max="35" width="52.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5">
+    <row r="1" spans="1:35" ht="31.5">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1699,18 +1903,71 @@
         <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="47.25">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="Q1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="T1" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="V1" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI1" s="30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>13</v>
@@ -1719,13 +1976,13 @@
         <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -1734,88 +1991,129 @@
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="Q2" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="47.25">
-      <c r="A3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="U2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="AB2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="AC2" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="AE2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="AG2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="AH2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    </row>
+    <row r="3" spans="1:35" ht="15.75">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="3"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+    </row>
+    <row r="4" spans="1:35">
       <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1">
+    <row r="6" spans="1:35" ht="24" customHeight="1">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:35">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:35">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:35">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:35">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:35">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:35">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:35">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:35">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:35">
       <c r="A15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{8B51A6DA-AB47-4D21-B79F-C0F5CD9F6D1E}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{7743F41D-75AB-44A3-B840-8FDE6759F018}"/>
+    <hyperlink ref="AB2" r:id="rId2" xr:uid="{E923A941-1476-48B8-9C52-7016F98272F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -1865,15 +2163,15 @@
         <v>21</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -1895,10 +2193,10 @@
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1954,7 +2252,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -1962,18 +2260,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1993,7 +2291,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2001,18 +2299,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2033,13 +2331,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>16</v>
@@ -2047,30 +2345,30 @@
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2093,46 +2391,46 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2162,44 +2460,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D4DFB8-6BD9-4F04-96F9-5B36C7F58D56}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F8B122-AEF3-4C28-9818-5BD8CEAC48AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="143">
   <si>
     <t>product_name</t>
   </si>
@@ -412,9 +412,6 @@
     <t>demo</t>
   </si>
   <si>
-    <t>testingsampletestingsample</t>
-  </si>
-  <si>
     <t>sampletesingg</t>
   </si>
   <si>
@@ -458,6 +455,24 @@
   </si>
   <si>
     <t>asdad</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>demoo</t>
+  </si>
+  <si>
+    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -1034,16 +1049,16 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="17" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>116</v>
@@ -1053,8 +1068,12 @@
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -1149,13 +1168,13 @@
         <v>70</v>
       </c>
       <c r="E2" s="27">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1745,7 +1764,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>121</v>
@@ -1923,43 +1942,43 @@
         <v>29</v>
       </c>
       <c r="U1" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="V1" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="V1" s="31" t="s">
-        <v>136</v>
-      </c>
       <c r="Y1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="AD1" s="10" t="s">
         <v>115</v>
       </c>
       <c r="AE1" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF1" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AI1" s="30" t="s">
         <v>132</v>
-      </c>
-      <c r="AI1" s="30" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="47.25">
@@ -2012,7 +2031,7 @@
         <v>98</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y2" s="11" t="s">
         <v>92</v>
@@ -2027,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AD2" s="11" t="s">
         <v>9</v>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F8B122-AEF3-4C28-9818-5BD8CEAC48AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAD38D8-C1F9-48C9-BC55-0806D595CB9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="14" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="139">
   <si>
     <t>product_name</t>
   </si>
@@ -82,9 +82,6 @@
     <t>India</t>
   </si>
   <si>
-    <t>black</t>
-  </si>
-  <si>
     <t>C:\Users\Suresh V\Desktop\automation\lena-denk-vO_RghTzvxE-unsplash(1).jpg</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>paper</t>
   </si>
   <si>
-    <t>plasticssss</t>
-  </si>
-  <si>
     <t>Print Audit Report</t>
   </si>
   <si>
@@ -364,9 +358,6 @@
     <t>samples</t>
   </si>
   <si>
-    <t>PRD2026X00022</t>
-  </si>
-  <si>
     <t>Weekly</t>
   </si>
   <si>
@@ -394,9 +385,6 @@
     <t>edit_status</t>
   </si>
   <si>
-    <t>testingsample</t>
-  </si>
-  <si>
     <t>2026-05-27</t>
   </si>
   <si>
@@ -412,9 +400,6 @@
     <t>demo</t>
   </si>
   <si>
-    <t>sampletesingg</t>
-  </si>
-  <si>
     <t>edit_product_name</t>
   </si>
   <si>
@@ -463,16 +448,19 @@
     <t>2026-06-08</t>
   </si>
   <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
   </si>
   <si>
-    <t>demoo</t>
-  </si>
-  <si>
-    <t>Inactive</t>
+    <t>poiuyt</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>PRD2026X0028</t>
+  </si>
+  <si>
+    <t>demotesting</t>
   </si>
 </sst>
 </file>
@@ -1015,65 +1003,61 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="G1" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>114</v>
-      </c>
       <c r="K1" s="31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="17" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>142</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="7"/>
       <c r="D3" s="3"/>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -1133,48 +1117,48 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" s="27">
         <v>46181</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1232,26 +1216,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1291,26 +1275,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1342,13 +1326,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>46</v>
-      </c>
-      <c r="C1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1359,7 +1343,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1377,12 +1361,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1406,24 +1390,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1443,39 +1427,39 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1500,10 +1484,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1511,10 +1495,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1559,30 +1543,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1625,33 +1609,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -1660,7 +1644,7 @@
         <v>9807529895</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1731,46 +1715,46 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="F1" s="36"/>
       <c r="G1" s="18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I1" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J1" s="35"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>138</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1805,30 +1789,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1910,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>5</v>
@@ -1922,86 +1906,86 @@
         <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>88</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>89</v>
       </c>
       <c r="N1" s="39"/>
       <c r="O1" s="39"/>
       <c r="Q1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="S1" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="T1" s="31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U1" s="31" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Y1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AI1" s="30" t="s">
         <v>127</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG1" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="AH1" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="AI1" s="30" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" s="11" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -2010,49 +1994,49 @@
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="Q2" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q2" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="U2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AA2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="12" t="s">
-        <v>14</v>
-      </c>
       <c r="AC2" s="11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AD2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AF2" s="11" t="s">
         <v>10</v>
@@ -2061,10 +2045,10 @@
         <v>11</v>
       </c>
       <c r="AH2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15.75">
@@ -2158,39 +2142,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="31.5">
       <c r="A1" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>21</v>
-      </c>
       <c r="I1" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -2206,16 +2190,16 @@
         <v>46374</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2271,7 +2255,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2279,18 +2263,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2310,7 +2294,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2318,18 +2302,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2350,44 +2334,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2410,46 +2394,46 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>41</v>
       </c>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2479,44 +2463,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>96</v>
-      </c>
       <c r="D2" s="26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="D3" s="26" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAD38D8-C1F9-48C9-BC55-0806D595CB9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AA6999-32FA-4823-83CC-8B917E036C88}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -451,16 +451,16 @@
     <t>2026-05-25</t>
   </si>
   <si>
-    <t>poiuyt</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>PRD2026X0028</t>
-  </si>
-  <si>
     <t>demotesting</t>
+  </si>
+  <si>
+    <t>poiuytr</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>PRD2026X0030</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
@@ -1040,16 +1040,16 @@
         <v>134</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
@@ -1738,17 +1738,17 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>117</v>
@@ -1979,7 +1979,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AA6999-32FA-4823-83CC-8B917E036C88}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2025836E-01F2-40FC-8D9E-7ED4ADAF3E4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="3" r:id="rId1"/>
@@ -115,352 +115,352 @@
     <t>Chennai, Tamil Nadu, India</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>variants_type</t>
+  </si>
+  <si>
+    <t>variants_value</t>
+  </si>
+  <si>
+    <t>search_value</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>iphone</t>
+  </si>
+  <si>
+    <t>samsung</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>sports shoes</t>
+  </si>
+  <si>
+    <t>B794-20</t>
+  </si>
+  <si>
+    <t>B794-15</t>
+  </si>
+  <si>
+    <t>M794-M01-RUF3000R1-brown</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>usermobile</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>testuser</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>Report_start_Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report_end_Id </t>
+  </si>
+  <si>
+    <t>select_user</t>
+  </si>
+  <si>
+    <t>Le beta (9619583752)</t>
+  </si>
+  <si>
+    <t>Bulk_Id</t>
+  </si>
+  <si>
+    <t>5000,5001,5002</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>report_name</t>
+  </si>
+  <si>
+    <t>select_format</t>
+  </si>
+  <si>
+    <t>select_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample </t>
+  </si>
+  <si>
+    <t>CSV</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>pass456</t>
+  </si>
+  <si>
+    <t>arivu22@mailinator.com</t>
+  </si>
+  <si>
+    <t>Admin@123</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>QR Code with Microtext and Invisible Text</t>
+  </si>
+  <si>
+    <t>sample123@gmail.com</t>
+  </si>
+  <si>
+    <t>test@123</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>select_report</t>
+  </si>
+  <si>
+    <t>mail_receiving_duration</t>
+  </si>
+  <si>
+    <t>date_string</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Role_name</t>
+  </si>
+  <si>
+    <t>User_type</t>
+  </si>
+  <si>
+    <t>Admin User - Manufacturer</t>
+  </si>
+  <si>
+    <t>search_name</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>select_Role</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mobile_number</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>Asdfg@123</t>
+  </si>
+  <si>
+    <t>QR_Type</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>image_format</t>
+  </si>
+  <si>
+    <t>B794-50</t>
+  </si>
+  <si>
+    <t>le beta</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>video_title</t>
+  </si>
+  <si>
+    <t>video_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testing </t>
+  </si>
+  <si>
+    <t>C:\Users\Suresh V\Downloads\20260505_094627.mp4</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>Print Audit Report</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>Bi-Weekly</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>mklpp</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>abcd128316790@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>Last 7 Days</t>
+  </si>
+  <si>
+    <t>XLSX</t>
+  </si>
+  <si>
+    <t>samples</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>print_audit_report</t>
+  </si>
+  <si>
+    <t>M19342-PRD2025X0012</t>
+  </si>
+  <si>
+    <t>filter_status</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>edit_category_name</t>
+  </si>
+  <si>
+    <t>edit_status</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>search_Category</t>
+  </si>
+  <si>
+    <t>edit_variants_type</t>
+  </si>
+  <si>
+    <t>edit_variants_value</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>edit_product_name</t>
+  </si>
+  <si>
+    <t>edit_brand_name</t>
+  </si>
+  <si>
+    <t>edit_upload_product_image</t>
+  </si>
+  <si>
+    <t>edit_product_url</t>
+  </si>
+  <si>
+    <t>edit_SKU_ID</t>
+  </si>
+  <si>
+    <t>edit_select_category</t>
+  </si>
+  <si>
+    <t>edit_description</t>
+  </si>
+  <si>
+    <t>edit_country</t>
+  </si>
+  <si>
+    <t>edit_video_title</t>
+  </si>
+  <si>
+    <t>edit_video_file</t>
+  </si>
+  <si>
+    <t>prdgvgftfg</t>
+  </si>
+  <si>
+    <t>filter_category</t>
+  </si>
+  <si>
+    <t>filter_created_by</t>
+  </si>
+  <si>
+    <t>asdad</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>demotesting</t>
+  </si>
+  <si>
+    <t>poiuytr</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>PRD2026X0030</t>
+  </si>
+  <si>
     <t>1.5 cm</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>variants_type</t>
-  </si>
-  <si>
-    <t>variants_value</t>
-  </si>
-  <si>
-    <t>search_value</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>iphone</t>
-  </si>
-  <si>
-    <t>samsung</t>
-  </si>
-  <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>sports shoes</t>
-  </si>
-  <si>
-    <t>B794-20</t>
-  </si>
-  <si>
-    <t>B794-15</t>
-  </si>
-  <si>
-    <t>M794-M01-RUF3000R1-brown</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>usermobile</t>
-  </si>
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>testuser</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>Report_start_Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report_end_Id </t>
-  </si>
-  <si>
-    <t>select_user</t>
-  </si>
-  <si>
-    <t>Le beta (9619583752)</t>
-  </si>
-  <si>
-    <t>Bulk_Id</t>
-  </si>
-  <si>
-    <t>5000,5001,5002</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>report_name</t>
-  </si>
-  <si>
-    <t>select_format</t>
-  </si>
-  <si>
-    <t>select_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample </t>
-  </si>
-  <si>
-    <t>CSV</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>admin2</t>
-  </si>
-  <si>
-    <t>pass456</t>
-  </si>
-  <si>
-    <t>arivu22@mailinator.com</t>
-  </si>
-  <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>QR Code with Microtext and Invisible Text</t>
-  </si>
-  <si>
-    <t>sample123@gmail.com</t>
-  </si>
-  <si>
-    <t>test@123</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>select_report</t>
-  </si>
-  <si>
-    <t>mail_receiving_duration</t>
-  </si>
-  <si>
-    <t>date_string</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Role_name</t>
-  </si>
-  <si>
-    <t>User_type</t>
-  </si>
-  <si>
-    <t>Admin User - Manufacturer</t>
-  </si>
-  <si>
-    <t>search_name</t>
-  </si>
-  <si>
-    <t>user_name</t>
-  </si>
-  <si>
-    <t>select_Role</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mobile_number</t>
-  </si>
-  <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>Asdfg@123</t>
-  </si>
-  <si>
-    <t>QR_Type</t>
-  </si>
-  <si>
-    <t>PDF</t>
-  </si>
-  <si>
-    <t>image_format</t>
-  </si>
-  <si>
-    <t>B794-50</t>
-  </si>
-  <si>
-    <t>le beta</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>video_title</t>
-  </si>
-  <si>
-    <t>video_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testing </t>
-  </si>
-  <si>
-    <t>C:\Users\Suresh V\Downloads\20260505_094627.mp4</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <t>Print Audit Report</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>Bi-Weekly</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>mklpp</t>
-  </si>
-  <si>
-    <t>sample</t>
-  </si>
-  <si>
-    <t>abcd128316790@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>Last 7 Days</t>
-  </si>
-  <si>
-    <t>XLSX</t>
-  </si>
-  <si>
-    <t>samples</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>print_audit_report</t>
-  </si>
-  <si>
-    <t>M19342-PRD2025X0012</t>
-  </si>
-  <si>
-    <t>filter_status</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>category_name</t>
-  </si>
-  <si>
-    <t>edit_category_name</t>
-  </si>
-  <si>
-    <t>edit_status</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>search_Category</t>
-  </si>
-  <si>
-    <t>edit_variants_type</t>
-  </si>
-  <si>
-    <t>edit_variants_value</t>
-  </si>
-  <si>
-    <t>demo</t>
-  </si>
-  <si>
-    <t>edit_product_name</t>
-  </si>
-  <si>
-    <t>edit_brand_name</t>
-  </si>
-  <si>
-    <t>edit_upload_product_image</t>
-  </si>
-  <si>
-    <t>edit_product_url</t>
-  </si>
-  <si>
-    <t>edit_SKU_ID</t>
-  </si>
-  <si>
-    <t>edit_select_category</t>
-  </si>
-  <si>
-    <t>edit_description</t>
-  </si>
-  <si>
-    <t>edit_country</t>
-  </si>
-  <si>
-    <t>edit_video_title</t>
-  </si>
-  <si>
-    <t>edit_video_file</t>
-  </si>
-  <si>
-    <t>prdgvgftfg</t>
-  </si>
-  <si>
-    <t>filter_category</t>
-  </si>
-  <si>
-    <t>filter_created_by</t>
-  </si>
-  <si>
-    <t>asdad</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>demotesting</t>
-  </si>
-  <si>
-    <t>poiuytr</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>PRD2026X0030</t>
   </si>
 </sst>
 </file>
@@ -1003,53 +1003,53 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="D1" s="18"/>
       <c r="E1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="G1" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="K1" s="31" t="s">
         <v>111</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
@@ -1117,48 +1117,48 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="27">
-        <v>46181</v>
+        <v>46216</v>
       </c>
       <c r="F2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1216,26 +1216,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1275,26 +1275,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1326,13 +1326,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1343,7 +1343,7 @@
         <v>6000</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1361,12 +1361,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1390,24 +1390,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
         <v>51</v>
-      </c>
-      <c r="B1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
         <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1427,39 +1427,39 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>63</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1484,10 +1484,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1543,30 +1543,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1609,33 +1609,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>97</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -1644,7 +1644,7 @@
         <v>9807529895</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1715,46 +1715,46 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="F1" s="36"/>
       <c r="G1" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="I1" s="38" t="s">
         <v>115</v>
-      </c>
-      <c r="I1" s="38" t="s">
-        <v>116</v>
       </c>
       <c r="J1" s="35"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1789,30 +1789,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1894,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>5</v>
@@ -1906,71 +1906,71 @@
         <v>8</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>87</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>88</v>
       </c>
       <c r="N1" s="39"/>
       <c r="O1" s="39"/>
       <c r="Q1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="S1" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T1" s="31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="V1" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="V1" s="31" t="s">
-        <v>130</v>
-      </c>
       <c r="Y1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="AD1" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AI1" s="30" t="s">
         <v>126</v>
-      </c>
-      <c r="AI1" s="30" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="47.25">
       <c r="A2" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>12</v>
@@ -1979,13 +1979,13 @@
         <v>13</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>10</v>
@@ -1994,34 +1994,34 @@
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="Q2" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="U2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA2" s="11" t="s">
         <v>12</v>
@@ -2030,13 +2030,13 @@
         <v>13</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AD2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AF2" s="11" t="s">
         <v>10</v>
@@ -2045,10 +2045,10 @@
         <v>11</v>
       </c>
       <c r="AH2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15.75">
@@ -2166,15 +2166,15 @@
         <v>20</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -2184,22 +2184,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="6">
-        <v>46162</v>
+        <v>46223</v>
       </c>
       <c r="F2" s="6">
         <v>46374</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2255,7 +2255,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2263,18 +2263,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2294,7 +2294,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
@@ -2302,18 +2302,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2334,13 +2334,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>15</v>
@@ -2348,30 +2348,30 @@
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2394,46 +2394,46 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>40</v>
       </c>
       <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="5">
         <v>9619583752</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="5">
         <v>9999999999</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2463,44 +2463,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2025836E-01F2-40FC-8D9E-7ED4ADAF3E4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AA5445-C6FD-4BF9-9ADB-CA290E40BB07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
@@ -364,103 +364,103 @@
     <t>print_audit_report</t>
   </si>
   <si>
+    <t>filter_status</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>edit_category_name</t>
+  </si>
+  <si>
+    <t>edit_status</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>search_Category</t>
+  </si>
+  <si>
+    <t>edit_variants_type</t>
+  </si>
+  <si>
+    <t>edit_variants_value</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>edit_product_name</t>
+  </si>
+  <si>
+    <t>edit_brand_name</t>
+  </si>
+  <si>
+    <t>edit_upload_product_image</t>
+  </si>
+  <si>
+    <t>edit_product_url</t>
+  </si>
+  <si>
+    <t>edit_SKU_ID</t>
+  </si>
+  <si>
+    <t>edit_select_category</t>
+  </si>
+  <si>
+    <t>edit_description</t>
+  </si>
+  <si>
+    <t>edit_country</t>
+  </si>
+  <si>
+    <t>edit_video_title</t>
+  </si>
+  <si>
+    <t>edit_video_file</t>
+  </si>
+  <si>
+    <t>prdgvgftfg</t>
+  </si>
+  <si>
+    <t>filter_category</t>
+  </si>
+  <si>
+    <t>filter_created_by</t>
+  </si>
+  <si>
+    <t>asdad</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>demotesting</t>
+  </si>
+  <si>
+    <t>poiuytr</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>PRD2026X0030</t>
+  </si>
+  <si>
+    <t>1.5 cm</t>
+  </si>
+  <si>
     <t>M19342-PRD2025X0012</t>
-  </si>
-  <si>
-    <t>filter_status</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>category_name</t>
-  </si>
-  <si>
-    <t>edit_category_name</t>
-  </si>
-  <si>
-    <t>edit_status</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>search_Category</t>
-  </si>
-  <si>
-    <t>edit_variants_type</t>
-  </si>
-  <si>
-    <t>edit_variants_value</t>
-  </si>
-  <si>
-    <t>demo</t>
-  </si>
-  <si>
-    <t>edit_product_name</t>
-  </si>
-  <si>
-    <t>edit_brand_name</t>
-  </si>
-  <si>
-    <t>edit_upload_product_image</t>
-  </si>
-  <si>
-    <t>edit_product_url</t>
-  </si>
-  <si>
-    <t>edit_SKU_ID</t>
-  </si>
-  <si>
-    <t>edit_select_category</t>
-  </si>
-  <si>
-    <t>edit_description</t>
-  </si>
-  <si>
-    <t>edit_country</t>
-  </si>
-  <si>
-    <t>edit_video_title</t>
-  </si>
-  <si>
-    <t>edit_video_file</t>
-  </si>
-  <si>
-    <t>prdgvgftfg</t>
-  </si>
-  <si>
-    <t>filter_category</t>
-  </si>
-  <si>
-    <t>filter_created_by</t>
-  </si>
-  <si>
-    <t>asdad</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>demotesting</t>
-  </si>
-  <si>
-    <t>poiuytr</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>PRD2026X0030</t>
-  </si>
-  <si>
-    <t>1.5 cm</t>
   </si>
 </sst>
 </file>
@@ -1016,40 +1016,40 @@
         <v>39</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H1" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="K1" s="31" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>9</v>
@@ -1155,10 +1155,10 @@
         <v>46216</v>
       </c>
       <c r="F2" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>131</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1725,33 +1725,33 @@
       </c>
       <c r="F1" s="36"/>
       <c r="G1" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="I1" s="38" t="s">
         <v>114</v>
-      </c>
-      <c r="I1" s="38" t="s">
-        <v>115</v>
       </c>
       <c r="J1" s="35"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>64</v>
@@ -1920,49 +1920,49 @@
         <v>39</v>
       </c>
       <c r="S1" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T1" s="31" t="s">
         <v>27</v>
       </c>
       <c r="U1" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="V1" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="V1" s="31" t="s">
-        <v>129</v>
-      </c>
       <c r="Y1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z1" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AD1" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AI1" s="30" t="s">
         <v>125</v>
-      </c>
-      <c r="AI1" s="30" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="47.25">
@@ -1979,7 +1979,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>9</v>
@@ -2000,10 +2000,10 @@
         <v>89</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>68</v>
@@ -2015,7 +2015,7 @@
         <v>95</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y2" s="11" t="s">
         <v>90</v>
@@ -2030,7 +2030,7 @@
         <v>13</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AD2" s="11" t="s">
         <v>9</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="2" spans="1:10" ht="30">
       <c r="A2" s="5" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="B2" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5">
@@ -2190,7 +2190,7 @@
         <v>46374</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>22</v>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AA5445-C6FD-4BF9-9ADB-CA290E40BB07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2146ECC-A727-404E-845B-101BA4C2F1F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
@@ -460,7 +460,7 @@
     <t>1.5 cm</t>
   </si>
   <si>
-    <t>M19342-PRD2025X0012</t>
+    <t>M19342-PRD2025X0013</t>
   </si>
 </sst>
 </file>
@@ -2177,14 +2177,14 @@
         <v>138</v>
       </c>
       <c r="B2" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="6">
-        <v>46223</v>
+        <v>46236</v>
       </c>
       <c r="F2" s="6">
         <v>46374</v>

--- a/mf_products_data.xlsx
+++ b/mf_products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh V\Desktop\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2146ECC-A727-404E-845B-101BA4C2F1F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC339D80-AA5C-47A0-8377-A57316DD84F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1E71232C-EF9C-4FE2-8681-349AE10419A2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="category" sheetId="3" r:id="rId1"/>
     <sheet name="variants" sheetId="4" r:id="rId2"/>
     <sheet name="products" sheetId="1" r:id="rId3"/>
-    <sheet name="Generate_QR" sheetId="2" r:id="rId4"/>
+    <sheet name="Request_QR_code" sheetId="2" r:id="rId4"/>
     <sheet name="Download_QR" sheetId="5" r:id="rId5"/>
     <sheet name="Invalidate_QR" sheetId="6" r:id="rId6"/>
     <sheet name="Reassign_Batch_QR" sheetId="7" r:id="rId7"/>
@@ -460,7 +460,7 @@
     <t>1.5 cm</t>
   </si>
   <si>
-    <t>M19342-PRD2025X0013</t>
+    <t>M19342-PRD2025X0012</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1152,7 @@
         <v>68</v>
       </c>
       <c r="E2" s="27">
-        <v>46216</v>
+        <v>46258</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>130</v>
@@ -2177,14 +2177,14 @@
         <v>138</v>
       </c>
       <c r="B2" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="6">
-        <v>46236</v>
+        <v>46255</v>
       </c>
       <c r="F2" s="6">
         <v>46374</v>
